--- a/output/DESPIECE_KITS_DASHBOARD.xlsx
+++ b/output/DESPIECE_KITS_DASHBOARD.xlsx
@@ -86,7 +86,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -108,6 +108,39 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -126,6 +159,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -135,8 +169,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -505,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K43"/>
+  <dimension ref="B2:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -515,10 +550,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
@@ -545,9 +576,10 @@
         </is>
       </c>
       <c r="F4" s="4">
-        <f>IFERROR(XLOOKUP(C4,Kits!A:A,Kits!B:B),"")</f>
+        <f>IFERROR(XLOOKUP(C4,Kits!A2:A13,Kits!B2:B13),"")</f>
         <v/>
       </c>
+      <c r="G4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -566,9 +598,10 @@
         </is>
       </c>
       <c r="F5" s="4">
-        <f>IFERROR(XLOOKUP(C4,Kits!A:A,Kits!C:C)&amp;" / "&amp;XLOOKUP(C4,Kits!A:A,Kits!D:D),"")</f>
+        <f>IFERROR(XLOOKUP(C4,Kits!A2:A13,Kits!C2:C13)&amp;" / "&amp;XLOOKUP(C4,Kits!A2:A13,Kits!D2:D13),"")</f>
         <v/>
       </c>
+      <c r="G5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -587,377 +620,340 @@
         </is>
       </c>
       <c r="F6" s="4">
-        <f>IFERROR(XLOOKUP(C4,Kits!A:A,Kits!E:E)&amp;" kW · "&amp;XLOOKUP(C4,Kits!A:A,Kits!F:F)&amp;" paneles","")</f>
+        <f>IFERROR(XLOOKUP(C4,Kits!A2:A13,Kits!E2:E13)&amp;" kW · "&amp;XLOOKUP(C4,Kits!A2:A13,Kits!F2:F13)&amp;" paneles","")</f>
         <v/>
       </c>
+      <c r="G6" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>COMPONENTES BASE DEL KIT</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Marca</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="7">
-        <f>FILTER(BOM_Base!C:G, BOM_Base!A:A=C4, "")</f>
+      <c r="B11" s="8">
+        <f t="array" ref="B11:F18">IFERROR(_xlfn._xlws.FILTER(BOM_Base!C2:G55,BOM_Base!A2:A55=C4,""),"")</f>
         <v/>
       </c>
       <c r="C11" s="4" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="n"/>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="4" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="7" t="n"/>
+      <c r="B13" s="8" t="n"/>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="7" t="n"/>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="4" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="7" t="n"/>
+      <c r="B15" s="8" t="n"/>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="7" t="n"/>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="4" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="7" t="n"/>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="4" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="7" t="n"/>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="4" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>ESTRUCTURA SELECCIONADA (SET)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Código Set</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="B22" s="7" t="n"/>
+      <c r="B22" s="8">
+        <f t="array" ref="B22:F23">IFERROR(_xlfn._xlws.FILTER(BOM_Estructura!C2:G37,(BOM_Estructura!A2:A37=C4)*(BOM_Estructura!B2:B37=C5),""),"")</f>
+        <v/>
+      </c>
       <c r="C22" s="4" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>ESTRUCTURA SELECCIONADA (SET)</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
+          <t>DESPIECE INTERNO DE LA ESTRUCTURA (por set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Set:</t>
+        </is>
+      </c>
+      <c r="C26" s="9">
+        <f>IFERROR(INDEX(BOM_Estructura!G2:G37,MATCH(1,(BOM_Estructura!A2:A37=C4)*(BOM_Estructura!B2:B37=C5),0)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Sets a usar:</t>
+        </is>
+      </c>
+      <c r="E26" s="9">
+        <f>IFERROR(INDEX(BOM_Estructura!C2:C37,MATCH(1,(BOM_Estructura!A2:A37=C4)*(BOM_Estructura!B2:B37=C5),0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Qty x set</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Qty Total</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="8">
+        <f t="array" ref="B28:B34">IFERROR(_xlfn._xlws.FILTER(Estructuras_Detalle!B2:B40,Estructuras_Detalle!A2:A40=C26,""),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="8">
+        <f t="array" ref="C28:C34">IFERROR(_xlfn._xlws.FILTER(Estructuras_Detalle!B2:B40,Estructuras_Detalle!A2:A40=C26,"")*E26,"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="4">
+        <f t="array" ref="D28:G34">IFERROR(_xlfn._xlws.FILTER(Estructuras_Detalle!C2:F40,Estructuras_Detalle!A2:A40=C26,""),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>SOPORTE BATERÍA (solo kits HV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>Marca</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="7">
-        <f>FILTER(BOM_Estructura!C:G, (BOM_Estructura!A:A=C4)*(BOM_Estructura!B:B=C5), "")</f>
+    <row r="38">
+      <c r="B38" s="8">
+        <f t="array" ref="B38:F39">IFERROR(_xlfn._xlws.FILTER(BOM_Soporte!C2:G9,(BOM_Soporte!A2:A9=C4)*(BOM_Soporte!B2:B9=C6),"N/A para este kit"),"N/A para este kit")</f>
         <v/>
       </c>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>DESPIECE INTERNO DE LA ESTRUCTURA (por set)</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>Set:</t>
-        </is>
-      </c>
-      <c r="I29" s="9">
-        <f>IFERROR(INDEX(BOM_Estructura!G:G, MATCH(1,(BOM_Estructura!A:A=C4)*(BOM_Estructura!B:B=C5),0)),"")</f>
-        <v/>
-      </c>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t>Sets:</t>
-        </is>
-      </c>
-      <c r="K29" s="9">
-        <f>IFERROR(INDEX(BOM_Estructura!C:C, MATCH(1,(BOM_Estructura!A:A=C4)*(BOM_Estructura!B:B=C5),0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Qty x set</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Qty Total</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Categoría</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>Código</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="7">
-        <f>IFERROR(FILTER(Estructuras_Detalle!B:B, Estructuras_Detalle!A:A=I29, ""),"")</f>
-        <v/>
-      </c>
-      <c r="C31" s="7">
-        <f>IFERROR(FILTER(Estructuras_Detalle!B:B, Estructuras_Detalle!A:A=I29, "")*K29,"")</f>
-        <v/>
-      </c>
-      <c r="D31" s="4">
-        <f>IFERROR(FILTER(Estructuras_Detalle!C:F, Estructuras_Detalle!A:A=I29, ""),"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>SOPORTE BATERÍA (solo kits HV)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Categoría</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>Código</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="7">
-        <f>IFERROR(FILTER(BOM_Soporte!C:G,(BOM_Soporte!A:A=C4)*(BOM_Soporte!B:B=C6),"N/A para este kit"),"N/A para este kit")</f>
-        <v/>
-      </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="7" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B24:G24"/>
+  <mergeCells count="8">
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="F5:G5"/>
     <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B25:G25"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -1030,7 +1026,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>EC-3K</t>
         </is>
@@ -1040,30 +1036,30 @@
           <t>Economy 3 kW</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Monofásica</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>On-Grid</t>
         </is>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="E2" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="F2" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>EC-5K</t>
         </is>
@@ -1073,30 +1069,30 @@
           <t>Economy Plus 5 kW</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>Monofásica</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>On-Grid</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E3" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>EC-6K</t>
         </is>
@@ -1106,30 +1102,30 @@
           <t>Economy Pro 6 kW</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Monofásica</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>On-Grid</t>
         </is>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>AC/R-3K</t>
         </is>
@@ -1139,30 +1135,30 @@
           <t>Always Connected / Rural 3 kW</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Monofásica</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Híbrido</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>AC/R-5K</t>
         </is>
@@ -1172,30 +1168,30 @@
           <t>Always Connected / Rural 5 kW</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Monofásica</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Híbrido</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>ECT-8K</t>
         </is>
@@ -1205,30 +1201,30 @@
           <t>Economy T 8 kW</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Trifásica</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>On-Grid</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>ECT-12K</t>
         </is>
@@ -1238,30 +1234,30 @@
           <t>Economy T Plus 12 kW</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Trifásica</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>On-Grid</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>ECT-20K</t>
         </is>
@@ -1271,30 +1267,30 @@
           <t>Economy T Pro 20 kW</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Trifásica</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>On-Grid</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>PS-8K</t>
         </is>
@@ -1304,30 +1300,30 @@
           <t>Power Station 8 kW</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Trifásica</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Híbrido</t>
         </is>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>PS-10K</t>
         </is>
@@ -1337,30 +1333,30 @@
           <t>Power Station Plus 10 kW</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Trifásica</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Híbrido</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>PS-12K</t>
         </is>
@@ -1370,30 +1366,30 @@
           <t>Power Station Pro 12 kW</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Trifásica</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Híbrido</t>
         </is>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>PS-15K</t>
         </is>
@@ -1403,23 +1399,23 @@
           <t>Power Station Mega 15 kW</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Trifásica</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Híbrido</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1486,17 +1482,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>EC-3K</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -1504,34 +1500,34 @@
           <t>Inversor Monofásico ON-GRID 3 kW</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Inverters</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>GW3000-XS-30</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>EC-3K</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="8" t="n">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1539,34 +1535,34 @@
           <t>Módulo Fotovoltaico TOPCon Bifacial 585w</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Paneles FV</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>TCL SOLAR</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>TCL-MI585DH182-72NT</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>EC-3K</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1574,34 +1570,34 @@
           <t>SET Cables + Conectores</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Cables</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>GENERICO</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>CC-20</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>EC-3K</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1609,34 +1605,34 @@
           <t>Smart Energy Controller Monofásico</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>GMK110</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>EC-5K</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1644,34 +1640,34 @@
           <t>Inversor Monofásico ON-GRID 5 kW</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Inverters</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>GW5000-MS-30</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>EC-5K</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>10</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1679,34 +1675,34 @@
           <t>Módulo Fotovoltaico TOPCon Bifacial 585w</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Paneles FV</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>TCL SOLAR</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>TCL-MI585DH182-72NT</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>EC-5K</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1714,34 +1710,34 @@
           <t>SET Cables + Conectores</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Cables</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>GENERICO</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>CC-20</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>EC-5K</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1749,34 +1745,34 @@
           <t>Smart Energy Controller Monofásico</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>GMK110</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>EC-6K</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1784,34 +1780,34 @@
           <t>Inversor Monofásico ON-GRID 6 kW</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>Inverters</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>GW6000-MS-30</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>EC-6K</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <v>12</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1819,34 +1815,34 @@
           <t>Módulo Fotovoltaico TOPCon Bifacial 585w</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Paneles FV</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>TCL SOLAR</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>TCL-MI585DH182-72NT</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>EC-6K</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1854,34 +1850,34 @@
           <t>SET Cables + Conectores</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Cables</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>GENERICO</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>CC-20</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>EC-6K</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1889,34 +1885,34 @@
           <t>Smart Energy Controller Monofásico</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>GMK110</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>AC/R-3K</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1924,34 +1920,34 @@
           <t>Inversor Monofásico HIBRIDO 3 kW</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Inverters</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>GW3000-ES-20</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>AC/R-3K</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="8" t="n">
         <v>6</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1959,34 +1955,34 @@
           <t>Módulo Fotovoltaico TOPCon Bifacial 585w</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Paneles FV</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>TCL SOLAR</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>TCL-MI585DH182-72NT</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>AC/R-3K</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1994,34 +1990,34 @@
           <t>SET Cables + Conectores</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>Cables</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>GENERICO</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>CC-20</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>AC/R-3K</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -2029,34 +2025,34 @@
           <t>Batería 5kWh - 48V (con supresión de fuego)</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Baterías</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>LX U5.0-30</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>AC/R-3K</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -2064,34 +2060,34 @@
           <t>Smart Energy Controller Monofásico</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>GMK110</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>AC/R-5K</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2099,34 +2095,34 @@
           <t>Inversor Monofásico HIBRIDO 5 kW</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Inverters</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>GW5000-ES-20</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>AC/R-5K</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="8" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -2134,34 +2130,34 @@
           <t>Módulo Fotovoltaico TOPCon Bifacial 585w</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>Paneles FV</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>TCL SOLAR</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>TCL-MI585DH182-72NT</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>AC/R-5K</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2169,34 +2165,34 @@
           <t>SET Cables + Conectores</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Cables</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>GENERICO</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>CC-20</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>AC/R-5K</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -2204,34 +2200,34 @@
           <t>Batería 5kWh - 48V (con supresión de fuego)</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Baterías</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>LX U5.0-30</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>AC/R-5K</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2239,34 +2235,34 @@
           <t>Smart Energy Controller Monofásico</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>GMK110</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>ECT-8K</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -2274,34 +2270,34 @@
           <t>Inversor Trifásico ON-GRID 8 kW</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Inverters</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>GW8000-SDT-30</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>ECT-8K</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="8" t="n">
         <v>16</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2309,34 +2305,34 @@
           <t>Módulo Fotovoltaico TOPCon Bifacial 585w</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Paneles FV</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>TCL SOLAR</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>TCL-MI585DH182-72NT</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>ECT-8K</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2344,34 +2340,34 @@
           <t>SET Cables + Conectores</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Cables</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>GENERICO</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>CC-20</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>ECT-8K</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2379,34 +2375,34 @@
           <t>Smart Energy Controller Trifásico</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>GMK330</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>ECT-12K</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2414,34 +2410,34 @@
           <t>Inversor Trifásico ON-GRID 12 kW</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>Inverters</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>GW12K-SDT-30</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>ECT-12K</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="8" t="n">
         <v>24</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2449,34 +2445,34 @@
           <t>Módulo Fotovoltaico TOPCon Bifacial 585w</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>Paneles FV</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>TCL SOLAR</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>TCL-MI585DH182-72NT</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>ECT-12K</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2484,34 +2480,34 @@
           <t>SET Cables + Conectores</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>Cables</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>GENERICO</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>CC-20</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>ECT-12K</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2519,34 +2515,34 @@
           <t>Smart Energy Controller Trifásico</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>GMK330</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>ECT-20K</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2554,34 +2550,34 @@
           <t>Inversor Trifásico ON-GRID 20 kW</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>Inverters</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>GW20K-SDT-30</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>ECT-20K</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="8" t="n">
         <v>40</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2589,34 +2585,34 @@
           <t>Módulo Fotovoltaico TOPCon Bifacial 585w</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>Paneles FV</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>TCL SOLAR</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>TCL-MI585DH182-72NT</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>ECT-20K</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2624,34 +2620,34 @@
           <t>SET Cables + Conectores</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>Cables</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>GENERICO</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>CC-20</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>ECT-20K</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2659,34 +2655,34 @@
           <t>Smart Energy Controller Trifásico</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>GMK330</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>PS-8K</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2694,34 +2690,34 @@
           <t>Inversor Trifásico HIBRIDO 8 kW</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>Inverters</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>GW8000-ET-20</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>PS-8K</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="8" t="n">
         <v>16</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2729,34 +2725,34 @@
           <t>Módulo Fotovoltaico TOPCon Bifacial 585w</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>Paneles FV</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>TCL SOLAR</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>TCL-MI585DH182-72NT</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>PS-8K</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2764,34 +2760,34 @@
           <t>SET Cables + Conectores</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>Cables</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>GENERICO</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>CC-20</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>PS-8K</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2799,34 +2795,34 @@
           <t>Batería Apilable 5kWh - HV</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>Baterías</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>LX D5.0-10</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>PS-8K</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2834,34 +2830,34 @@
           <t>Smart Energy Controller Trifásico</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>GMK330</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>PS-10K</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2869,34 +2865,34 @@
           <t>Inversor Trifásico HIBRIDO 10 kW</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>Inverters</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>GW10K-ET-20</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>PS-10K</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="8" t="n">
         <v>18</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2904,34 +2900,34 @@
           <t>Módulo Fotovoltaico TOPCon Bifacial 585w</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>Paneles FV</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>TCL SOLAR</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>TCL-MI585DH182-72NT</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>PS-10K</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2939,34 +2935,34 @@
           <t>SET Cables + Conectores</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>Cables</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>GENERICO</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>CC-20</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>PS-10K</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2974,34 +2970,34 @@
           <t>Batería Apilable 5kWh - HV</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>Baterías</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>LX D5.0-10</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>PS-10K</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3009,34 +3005,34 @@
           <t>Smart Energy Controller Trifásico</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>GMK330</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>PS-12K</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3044,34 +3040,34 @@
           <t>Inversor Trifásico HIBRIDO 12 kW</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>Inverters</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>GW12K-ET-20</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>PS-12K</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="8" t="n">
         <v>24</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3079,34 +3075,34 @@
           <t>Módulo Fotovoltaico TOPCon Bifacial 585w</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t>Paneles FV</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
         <is>
           <t>TCL SOLAR</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>TCL-MI585DH182-72NT</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>PS-12K</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3114,34 +3110,34 @@
           <t>SET Cables + Conectores</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>Cables</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>GENERICO</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>CC-20</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>PS-12K</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3149,34 +3145,34 @@
           <t>Batería Apilable 5kWh - HV</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>Baterías</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>LX D5.0-10</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>PS-12K</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3184,34 +3180,34 @@
           <t>Smart Energy Controller Trifásico</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>GMK330</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>PS-15K</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3219,34 +3215,34 @@
           <t>Inversor Trifásico HIBRIDO 15 kW</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>Inverters</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>GW15K-ET-20</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>PS-15K</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="8" t="n">
         <v>32</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3254,34 +3250,34 @@
           <t>Módulo Fotovoltaico TOPCon Bifacial 585w</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>Paneles FV</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>TCL SOLAR</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>TCL-MI585DH182-72NT</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>PS-15K</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3289,34 +3285,34 @@
           <t>SET Cables + Conectores</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>Cables</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>GENERICO</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>CC-20</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>PS-15K</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3324,34 +3320,34 @@
           <t>Batería Apilable 5kWh - HV</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>Baterías</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>LX D5.0-10</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>PS-15K</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3359,17 +3355,17 @@
           <t>Smart Energy Controller Trifásico</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>GOODWE</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>GMK330</t>
         </is>
@@ -3431,22 +3427,22 @@
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>Código</t>
+          <t>Código Set</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>EC-3K</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Chapa</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -3454,34 +3450,34 @@
           <t>Set Estructuras Techo Coplanar Chapa (x6)</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>C-6U</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>EC-3K</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Teja</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -3489,34 +3485,34 @@
           <t>Set Estructuras Techo Coplanar Teja (x6)</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>T-6U</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>EC-3K</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Suelo/Losa</t>
         </is>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -3524,34 +3520,34 @@
           <t>Set Estructuras Suelo / Losa (x6)</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>SL-6U</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>EC-5K</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Chapa</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -3559,34 +3555,34 @@
           <t>Set Estructuras Techo Coplanar Chapa (x5)</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>C-5U</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>EC-5K</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Teja</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3594,34 +3590,34 @@
           <t>Set Estructuras Techo Coplanar Teja (x5)</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>T-5U</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>EC-5K</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Suelo/Losa</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -3629,34 +3625,34 @@
           <t>Set Estructuras Suelo / Losa (x5)</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>SL-5U</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>EC-6K</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Chapa</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -3664,34 +3660,34 @@
           <t>Set Estructuras Techo Coplanar Chapa (x6)</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>C-6U</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>EC-6K</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Teja</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -3699,34 +3695,34 @@
           <t>Set Estructuras Techo Coplanar Teja (x6)</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>T-6U</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>EC-6K</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Suelo/Losa</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -3734,34 +3730,34 @@
           <t>Set Estructuras Suelo / Losa (x6)</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>SL-6U</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>AC/R-3K</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Chapa</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -3769,34 +3765,34 @@
           <t>Set Estructuras Techo Coplanar Chapa (x6)</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>C-6U</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>AC/R-3K</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Teja</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -3804,34 +3800,34 @@
           <t>Set Estructuras Techo Coplanar Teja (x6)</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>T-6U</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>AC/R-3K</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Suelo/Losa</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -3839,34 +3835,34 @@
           <t>Set Estructuras Suelo / Losa (x6)</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>SL-6U</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>AC/R-5K</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Chapa</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -3874,34 +3870,34 @@
           <t>Set Estructuras Techo Coplanar Chapa (x6)</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>C-6U</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>AC/R-5K</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Teja</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -3909,34 +3905,34 @@
           <t>Set Estructuras Techo Coplanar Teja (x6)</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>T-6U</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>AC/R-5K</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Suelo/Losa</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -3944,34 +3940,34 @@
           <t>Set Estructuras Suelo / Losa (x6)</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>SL-6U</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>ECT-8K</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Chapa</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -3979,34 +3975,34 @@
           <t>Set Estructuras Techo Coplanar Chapa (x8)</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>C-8U</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>ECT-8K</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Teja</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -4014,34 +4010,34 @@
           <t>Set Estructuras Techo Coplanar Teja (x8)</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>T-8U</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>ECT-8K</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Suelo/Losa</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -4049,34 +4045,34 @@
           <t>Set Estructuras Suelo / Losa (x8)</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>SL-8U</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>ECT-12K</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Chapa</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -4084,34 +4080,34 @@
           <t>Set Estructuras Techo Coplanar Chapa (x6)</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>C-6U</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>ECT-12K</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Teja</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -4119,34 +4115,34 @@
           <t>Set Estructuras Techo Coplanar Teja (x6)</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>T-6U</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>ECT-12K</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Suelo/Losa</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -4154,34 +4150,34 @@
           <t>Set Estructuras Suelo / Losa (x6)</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>SL-6U</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>ECT-20K</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Chapa</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -4189,34 +4185,34 @@
           <t>Set Estructuras Techo Coplanar Chapa (x8)</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>C-8U</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>ECT-20K</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Teja</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -4224,34 +4220,34 @@
           <t>Set Estructuras Techo Coplanar Teja (x8)</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>T-8U</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>ECT-20K</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Suelo/Losa</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -4259,34 +4255,34 @@
           <t>Set Estructuras Suelo / Losa (x8)</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>SL-8U</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>PS-8K</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Chapa</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -4294,34 +4290,34 @@
           <t>Set Estructuras Techo Coplanar Chapa (x8)</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>C-8U</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>PS-8K</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Teja</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -4329,34 +4325,34 @@
           <t>Set Estructuras Techo Coplanar Teja (x8)</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>T-8U</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>PS-8K</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Suelo/Losa</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -4364,34 +4360,34 @@
           <t>Set Estructuras Suelo / Losa (x8)</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>SL-8U</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>PS-10K</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Chapa</t>
         </is>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -4399,34 +4395,34 @@
           <t>Set Estructuras Techo Coplanar Chapa (x6)</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>C-6U</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>PS-10K</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Teja</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -4434,34 +4430,34 @@
           <t>Set Estructuras Techo Coplanar Teja (x6)</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>T-6U</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>PS-10K</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Suelo/Losa</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -4469,34 +4465,34 @@
           <t>Set Estructuras Suelo / Losa (x6)</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>SL-6U</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>PS-12K</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Chapa</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -4504,34 +4500,34 @@
           <t>Set Estructuras Techo Coplanar Chapa (x6)</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>C-6U</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>PS-12K</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Teja</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -4539,34 +4535,34 @@
           <t>Set Estructuras Techo Coplanar Teja (x6)</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>T-6U</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>PS-12K</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Suelo/Losa</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -4574,34 +4570,34 @@
           <t>Set Estructuras Suelo / Losa (x6)</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>SL-6U</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>PS-15K</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Chapa</t>
         </is>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -4609,34 +4605,34 @@
           <t>Set Estructuras Techo Coplanar Chapa (x8)</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>C-8U</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>PS-15K</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Teja</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -4644,34 +4640,34 @@
           <t>Set Estructuras Techo Coplanar Teja (x8)</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>T-8U</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>PS-15K</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Suelo/Losa</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -4679,17 +4675,17 @@
           <t>Set Estructuras Suelo / Losa (x8)</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>SL-8U</t>
         </is>
@@ -4756,17 +4752,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>PS-8K</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Pared</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -4774,34 +4770,34 @@
           <t>Soporte batería Lynx D para pared</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Hanger assembly for Lynx D</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>PS-8K</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Suelo</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -4809,34 +4805,34 @@
           <t>Base batería Lynx D para suelo</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Base assembly for Lynx D</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>PS-10K</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Pared</t>
         </is>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -4844,34 +4840,34 @@
           <t>Soporte batería Lynx D para pared</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Hanger assembly for Lynx D</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>PS-10K</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Suelo</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -4879,34 +4875,34 @@
           <t>Base batería Lynx D para suelo</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Base assembly for Lynx D</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>PS-12K</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Pared</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -4914,34 +4910,34 @@
           <t>Soporte batería Lynx D para pared</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Hanger assembly for Lynx D</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>PS-12K</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Suelo</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -4949,34 +4945,34 @@
           <t>Base batería Lynx D para suelo</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Base assembly for Lynx D</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>PS-15K</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Pared</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -4984,34 +4980,34 @@
           <t>Soporte batería Lynx D para pared</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Hanger assembly for Lynx D</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>PS-15K</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Suelo</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -5019,17 +5015,17 @@
           <t>Base batería Lynx D para suelo</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Base assembly for Lynx D</t>
         </is>
@@ -5090,12 +5086,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>C-5U</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="8" t="n">
         <v>12</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -5103,29 +5099,29 @@
           <t>MiniMET 0.5m Mini Riel Solarmet</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>NESTMNR050</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>C-5U</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5133,29 +5129,29 @@
           <t>Kit Anclajes Laterales</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>NESTSKITAL</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>C-5U</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -5163,29 +5159,29 @@
           <t>Kit Anclajes Medios - 4 Paneles</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>NESTSKITM4</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>C-6U</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -5193,29 +5189,29 @@
           <t>MiniMET 0.5m Mini Riel Solarmet</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>NESTMNR050</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>C-6U</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -5223,29 +5219,29 @@
           <t>Kit Anclajes Laterales</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>NESTSKITAL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>C-6U</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -5253,29 +5249,29 @@
           <t>Kit Anclajes Medios - 4 Paneles</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>NESTSKITM4</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>C-8U</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <v>18</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -5283,29 +5279,29 @@
           <t>MiniMET 0.5m Mini Riel Solarmet</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>NESTMNR050</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>C-8U</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -5313,29 +5309,29 @@
           <t>Kit Anclajes Laterales</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>NESTSKITAL</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>C-8U</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -5343,29 +5339,29 @@
           <t>Kit Anclajes Medios - 4 Paneles</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>NESTSKITM4</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>T-5U</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -5373,29 +5369,29 @@
           <t>Perfil CODA N2 (3.55m)</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>NESTSCO35D</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>T-5U</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -5403,29 +5399,29 @@
           <t>Anclaje Teja V2</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>NESTSTEJA1</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>T-5U</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -5433,29 +5429,29 @@
           <t>Kit Anclajes Laterales</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>NESTSKITAL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>T-5U</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -5463,29 +5459,29 @@
           <t>Kit Anclajes Medios - 4 Paneles</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>NESTSKITM4</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>T-5U</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -5493,29 +5489,29 @@
           <t>Kit Conexion CODA N2</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>NESTSKITCX</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>T-6U</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -5523,29 +5519,29 @@
           <t>Perfil CODA N2 (3.55m)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>NESTSCO35D</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>T-6U</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -5553,29 +5549,29 @@
           <t>Anclaje Teja V2</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>NESTSTEJA1</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>T-6U</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -5583,29 +5579,29 @@
           <t>Kit Anclajes Laterales</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>NESTSKITAL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>T-6U</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -5613,29 +5609,29 @@
           <t>Kit Anclajes Medios - 4 Paneles</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>NESTSKITM4</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>T-6U</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -5643,29 +5639,29 @@
           <t>Kit Conexion CODA N2</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>NESTSKITCX</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>T-8U</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -5673,29 +5669,29 @@
           <t>Perfil CODA N2 (3.55m)</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>NESTSCO35D</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>T-8U</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B22" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -5703,29 +5699,29 @@
           <t>Anclaje Teja V2</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>NESTSTEJA1</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>T-8U</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -5733,29 +5729,29 @@
           <t>Kit Anclajes Laterales</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>NESTSKITAL</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>T-8U</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B24" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -5763,29 +5759,29 @@
           <t>Kit Anclajes Medios - 4 Paneles</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>NESTSKITM4</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>T-8U</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -5793,29 +5789,29 @@
           <t>Kit Conexion CODA N2</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>NESTSKITCX</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>SL-5U</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B26" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -5823,29 +5819,29 @@
           <t>Perfil CODA N2 (4.75m) V2</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>IESTSCO47D</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>SL-5U</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n">
+      <c r="B27" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -5853,29 +5849,29 @@
           <t>Kit Anclajes Laterales</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>NESTSKITAL</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>SL-5U</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="B28" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -5883,29 +5879,29 @@
           <t>Kit Anclajes Medios - 4 Paneles</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>NESTSKITM4</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>SL-5U</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n">
+      <c r="B29" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -5913,29 +5909,29 @@
           <t>Kit Conexion CODA N2</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>NESTSKITCX</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>SL-5U</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
+      <c r="B30" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -5943,29 +5939,29 @@
           <t>Triangulo Aluminio Regulable</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>NESTSTRIAN</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>SL-6U</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n">
+      <c r="B31" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -5973,29 +5969,29 @@
           <t>Perfil CODA N2 (4.75m) V2</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>IESTSCO47D</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>SL-6U</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n">
+      <c r="B32" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -6003,29 +5999,29 @@
           <t>Kit Anclajes Laterales</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>NESTSKITAL</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>SL-6U</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n">
+      <c r="B33" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -6033,29 +6029,29 @@
           <t>Kit Anclajes Medios - 4 Paneles</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>NESTSKITM4</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>SL-6U</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
+      <c r="B34" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -6063,29 +6059,29 @@
           <t>Kit Conexion CODA N2</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>NESTSKITCX</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>SL-6U</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n">
+      <c r="B35" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -6093,29 +6089,29 @@
           <t>Triangulo Aluminio Regulable</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>NESTSTRIAN</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>SL-8U</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
+      <c r="B36" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -6123,29 +6119,29 @@
           <t>Perfil CODA N2 (4.75m) V2</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>IESTSCO47D</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>SL-8U</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
+      <c r="B37" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -6153,29 +6149,29 @@
           <t>Kit Anclajes Laterales</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>NESTSKITAL</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>SL-8U</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n">
+      <c r="B38" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -6183,29 +6179,29 @@
           <t>Kit Anclajes Medios - 4 Paneles</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>NESTSKITM4</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>SL-8U</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
+      <c r="B39" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -6213,29 +6209,29 @@
           <t>Kit Conexion CODA N2</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>NESTSKITCX</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>SL-8U</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n">
+      <c r="B40" s="8" t="n">
         <v>7</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -6243,17 +6239,17 @@
           <t>Triangulo Aluminio Regulable</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Estructuras</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>SOLARMET</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>NESTSTRIAN</t>
         </is>
@@ -6270,8 +6266,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
@@ -6291,7 +6293,667 @@
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>Descripción</t>
+          <t>Descripción del Componente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Paneles FV</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>TCL SOLAR</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>TCL-MI585DH182-72NT</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Módulo Fotovoltaico TOPCon Bifacial 585w</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Inverters</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>GW3000-XS-30</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Inversor Monofásico ON-GRID 3 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Inverters</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>GW3000-ES-20</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Inversor Monofásico HIBRIDO 3 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Inverters</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>GW5000-MS-30</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Inversor Monofásico ON-GRID 5 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Inverters</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>GW5000-ES-20</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Inversor Monofásico HIBRIDO 5 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Inverters</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>GW6000-MS-30</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Inversor Monofásico ON-GRID 6 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Inverters</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>GW8000-SDT-30</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Inversor Trifásico ON-GRID 8 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Inverters</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>GW8000-ET-20</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Inversor Trifásico HIBRIDO 8 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Inverters</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>GW10K-ET-20</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Inversor Trifásico HIBRIDO 10 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Inverters</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>GW12K-SDT-30</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Inversor Trifásico ON-GRID 12 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Inverters</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>GW12K-ET-20</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Inversor Trifásico HIBRIDO 12 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Inverters</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>GW15K-ET-20</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Inversor Trifásico HIBRIDO 15 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Inverters</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>GW20K-SDT-30</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Inversor Trifásico ON-GRID 20 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Baterías</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>LX U5.0-30</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Batería 5kWh - 48V (with fire suppression)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Baterías</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>LX D5.0-10</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Batería Apilable 5kWh - HV</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Accesorios</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>GMK110</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Smart Energy Controller Monofásico</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Accesorios</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>GMK330</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Smart Energy Controller Trifásico</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Accesorios</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Hanger assembly for Lynx D</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Soporte batería Lynx D para pared</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Accesorios</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>GOODWE</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Base assembly for Lynx D</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Base batería Lynx D para suelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>NESTMNR050</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>MiniMET 0.5m Mini Riel Solarmet</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>NESTSKITAL</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Kit Anclajes Laterales</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>NESTSKITM4</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Kit Anclajes Medios - 4 Paneles</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>NESTSCO35D</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Perfil CODA N2 (3.55m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>NESTSTEJA1</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Anclaje Teja V2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>NESTSKITCX</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Kit Conexion CODA N2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>IESTSCO47D</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Perfil CODA N2 (4.75m) V2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Estructuras</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>SOLARMET</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>NESTSTRIAN</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Triangulo Aluminio Regulable</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Cables</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Par Conector Macho-Hembra MC4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Cables</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Cable solar x 6mm2 (x metro) - Color Rojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Cables</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Cable solar x 6mm2 (x metro) - Color Negro</t>
         </is>
       </c>
     </row>
